--- a/Ruas de Bauru.xlsx
+++ b/Ruas de Bauru.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/09f6c07718b65a17/Trabalho/ATA Bauru/Site Recape Bauru/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD3D68E-8633-4E81-9CBB-8DAF6E18CC92}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97F604B6-7D39-1144-B319-556416380344}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLAN" sheetId="1" r:id="rId1"/>
@@ -891,10 +891,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1075,7 +1071,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L164"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1085,11 +1081,12 @@
     <col min="6" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1124,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1165,7 +1162,7 @@
         <v>414238.74800000002</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1199,7 +1196,7 @@
         <v>306249.08</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1233,7 +1230,7 @@
         <v>356730.17</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1267,7 +1264,7 @@
         <v>286363.38</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1301,7 +1298,7 @@
         <v>260373.8</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1335,7 +1332,7 @@
         <v>258040.94</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1369,7 +1366,7 @@
         <v>259128.07</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1403,7 +1400,7 @@
         <v>218573.14</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1437,7 +1434,7 @@
         <v>201099.51999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1471,7 +1468,7 @@
         <v>185431.94</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1505,7 +1502,7 @@
         <v>128974.65</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1537,7 +1534,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1569,7 +1566,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1601,7 +1598,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1639,7 +1636,7 @@
         <v>9408.8097999999882</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1677,7 +1674,7 @@
         <v>193096.22000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1711,7 +1708,7 @@
         <v>132520.51</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1751,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1791,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1831,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1871,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1911,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1949,7 +1946,7 @@
         <v>55152.118000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1987,7 +1984,7 @@
         <v>5985.0716000000248</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2027,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2067,7 +2064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2107,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2147,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2187,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2227,7 +2224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2267,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2301,7 +2298,7 @@
         <v>12971.24</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2341,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2379,7 +2376,7 @@
         <v>64977.121999999974</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2417,7 +2414,7 @@
         <v>107280.33600000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2449,7 +2446,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2481,7 +2478,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2515,7 +2512,7 @@
         <v>165383.5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2549,7 +2546,7 @@
         <v>102730.08</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2581,7 +2578,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2613,7 +2610,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2647,7 +2644,7 @@
         <v>102673.41</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2679,7 +2676,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2711,7 +2708,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2743,7 +2740,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2775,7 +2772,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2807,7 +2804,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2839,7 +2836,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2871,7 +2868,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2903,7 +2900,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2935,7 +2932,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2967,7 +2964,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2999,7 +2996,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3031,7 +3028,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3063,7 +3060,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3095,7 +3092,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3127,7 +3124,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3159,7 +3156,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3191,7 +3188,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3223,7 +3220,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3255,7 +3252,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3287,7 +3284,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -3319,7 +3316,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3351,7 +3348,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3383,7 +3380,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3415,7 +3412,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3447,7 +3444,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3479,7 +3476,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3511,7 +3508,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -3543,7 +3540,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -3575,7 +3572,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3607,7 +3604,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3639,7 +3636,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -3671,7 +3668,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -3703,7 +3700,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3735,7 +3732,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3767,7 +3764,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3799,7 +3796,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3831,7 +3828,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3863,7 +3860,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3895,7 +3892,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3927,7 +3924,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3959,7 +3956,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3991,7 +3988,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -4023,7 +4020,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -4055,7 +4052,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -4087,7 +4084,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4119,7 +4116,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -4151,7 +4148,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -4183,7 +4180,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4215,7 +4212,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4247,7 +4244,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4279,7 +4276,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4311,7 +4308,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4343,7 +4340,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4375,7 +4372,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4407,7 +4404,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -4439,7 +4436,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -4471,7 +4468,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -4503,7 +4500,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -4535,7 +4532,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4567,7 +4564,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -4599,7 +4596,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4631,7 +4628,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -4663,7 +4660,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4695,7 +4692,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -4727,7 +4724,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4759,7 +4756,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -4791,7 +4788,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4823,7 +4820,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -4855,7 +4852,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4887,7 +4884,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -4919,7 +4916,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4951,7 +4948,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -4983,7 +4980,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -5015,7 +5012,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -5047,7 +5044,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -5079,7 +5076,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -5111,7 +5108,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -5143,7 +5140,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -5175,7 +5172,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -5207,7 +5204,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -5239,7 +5236,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -5271,7 +5268,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -5303,7 +5300,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -5335,7 +5332,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5367,7 +5364,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -5399,7 +5396,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5431,7 +5428,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -5463,7 +5460,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -5495,7 +5492,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -5527,7 +5524,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -5559,7 +5556,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -5591,7 +5588,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -5623,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -5655,7 +5652,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -5687,7 +5684,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -5719,7 +5716,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -5751,7 +5748,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -5783,7 +5780,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -5815,7 +5812,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -5847,7 +5844,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -5879,7 +5876,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -5911,7 +5908,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -5943,7 +5940,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -5975,7 +5972,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -6007,7 +6004,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -6039,7 +6036,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -6071,7 +6068,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -6103,7 +6100,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -6135,7 +6132,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -6167,7 +6164,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -6199,7 +6196,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -6231,7 +6228,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -6263,7 +6260,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -6295,7 +6292,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -6327,7 +6324,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -6359,7 +6356,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -6391,7 +6388,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -6423,7 +6420,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -6455,7 +6452,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -6487,7 +6484,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -6535,99 +6532,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
     </row>
-    <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
     </row>
-    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="11"/>
     </row>
-    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="11"/>
     </row>
-    <row r="16" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>193</v>
       </c>

--- a/Ruas de Bauru.xlsx
+++ b/Ruas de Bauru.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/09f6c07718b65a17/Trabalho/ATA Bauru/Site Recape Bauru/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C182F9BA-A098-E84F-9F15-2526F5260513}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8308C60F-614A-8E4D-93DF-43D247D88F16}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="200">
   <si>
     <t>Item</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>Saldo a Medir (R$)</t>
+  </si>
+  <si>
+    <t>Paralisada</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1524,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -1553,7 +1556,7 @@
         <v>12</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -1585,7 +1588,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -2435,7 +2438,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -2467,7 +2470,7 @@
         <v>12</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -2567,7 +2570,7 @@
         <v>12</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -2599,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -2665,7 +2668,7 @@
         <v>12</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>13</v>
+        <v>199</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>

--- a/Ruas de Bauru.xlsx
+++ b/Ruas de Bauru.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/09f6c07718b65a17/Trabalho/ATA Bauru/Site Recape Bauru/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8308C60F-614A-8E4D-93DF-43D247D88F16}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CCB57FE-EF21-3A4C-87EB-8CDB066B39BD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1143,15 +1143,15 @@
         <v>591769.64</v>
       </c>
       <c r="J2" s="13">
-        <v>0.7</v>
+        <v>0.92579999999999996</v>
       </c>
       <c r="K2" s="14">
-        <f t="shared" ref="K2:K65" si="0">IF($I2="","",$I2*$J2)</f>
-        <v>414238.74799999996</v>
+        <f t="shared" ref="K2:K43" si="0">IF($I2="","",$I2*$J2)</f>
+        <v>547860.332712</v>
       </c>
       <c r="L2" s="14">
-        <f t="shared" ref="L2:L65" si="1">IF($I2="","",$I2-$K2)</f>
-        <v>177530.89200000005</v>
+        <f t="shared" ref="L2:L43" si="1">IF($I2="","",$I2-$K2)</f>
+        <v>43909.307288000011</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1168,24 +1168,28 @@
         <v>12</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46268</v>
+      </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="11">
+        <v>3110.08</v>
+      </c>
       <c r="I3" s="12">
         <v>306249.08</v>
       </c>
       <c r="J3" s="13">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15312.454000000002</v>
       </c>
       <c r="L3" s="14">
         <f t="shared" si="1"/>
-        <v>306249.08</v>
+        <v>290936.62599999999</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1215,15 +1219,15 @@
         <v>356730.17</v>
       </c>
       <c r="J4" s="13">
-        <v>0.4</v>
+        <v>0.97719999999999996</v>
       </c>
       <c r="K4" s="14">
         <f t="shared" si="0"/>
-        <v>142692.068</v>
+        <v>348596.72212399996</v>
       </c>
       <c r="L4" s="14">
         <f t="shared" si="1"/>
-        <v>214038.10199999998</v>
+        <v>8133.4478760000202</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1240,24 +1244,28 @@
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46268</v>
+      </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="15"/>
+      <c r="H5" s="11">
+        <v>3182.97</v>
+      </c>
       <c r="I5" s="12">
         <v>286363.38</v>
       </c>
       <c r="J5" s="13">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K5" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>71590.845000000001</v>
       </c>
       <c r="L5" s="14">
         <f t="shared" si="1"/>
-        <v>286363.38</v>
+        <v>214772.535</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="28" x14ac:dyDescent="0.2">
@@ -1274,24 +1282,28 @@
         <v>12</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46269</v>
+      </c>
       <c r="G6" s="7"/>
-      <c r="H6" s="15"/>
+      <c r="H6" s="11">
+        <v>3057.54</v>
+      </c>
       <c r="I6" s="12">
         <v>260373.8</v>
       </c>
       <c r="J6" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K6" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26037.38</v>
       </c>
       <c r="L6" s="14">
         <f t="shared" si="1"/>
-        <v>260373.8</v>
+        <v>234336.41999999998</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1308,24 +1320,28 @@
         <v>12</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46269</v>
+      </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="11">
+        <v>3090.14</v>
+      </c>
       <c r="I7" s="12">
         <v>258040.94</v>
       </c>
       <c r="J7" s="13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K7" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>77412.281999999992</v>
       </c>
       <c r="L7" s="14">
         <f t="shared" si="1"/>
-        <v>258040.94</v>
+        <v>180628.658</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1342,24 +1358,28 @@
         <v>12</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46269</v>
+      </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="11">
+        <v>3090.02</v>
+      </c>
       <c r="I8" s="12">
         <v>259128.07</v>
       </c>
       <c r="J8" s="13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K8" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>77738.421000000002</v>
       </c>
       <c r="L8" s="14">
         <f t="shared" si="1"/>
-        <v>259128.07</v>
+        <v>181389.649</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1376,24 +1396,28 @@
         <v>12</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46269</v>
+      </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="11">
+        <v>2576.75</v>
+      </c>
       <c r="I9" s="12">
         <v>218573.14</v>
       </c>
       <c r="J9" s="13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K9" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>65571.941999999995</v>
       </c>
       <c r="L9" s="14">
         <f t="shared" si="1"/>
-        <v>218573.14</v>
+        <v>153001.19800000003</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28" x14ac:dyDescent="0.2">
@@ -1423,15 +1447,15 @@
         <v>201099.51999999999</v>
       </c>
       <c r="J10" s="13">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="K10" s="14">
         <f t="shared" si="0"/>
-        <v>40219.904000000002</v>
+        <v>160879.61600000001</v>
       </c>
       <c r="L10" s="14">
         <f t="shared" si="1"/>
-        <v>160879.61599999998</v>
+        <v>40219.90399999998</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28" x14ac:dyDescent="0.2">
@@ -1486,12 +1510,14 @@
         <v>12</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F12" s="7">
         <v>46261</v>
       </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="7">
+        <v>46269</v>
+      </c>
       <c r="H12" s="11">
         <v>1334.5</v>
       </c>
@@ -1499,15 +1525,15 @@
         <v>128974.65</v>
       </c>
       <c r="J12" s="13">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="K12" s="14">
         <f t="shared" si="0"/>
-        <v>51589.86</v>
+        <v>128974.65</v>
       </c>
       <c r="L12" s="14">
         <f t="shared" si="1"/>
-        <v>77384.789999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1524,7 +1550,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -1556,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -1588,7 +1614,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -2502,24 +2528,28 @@
         <v>12</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F39" s="7">
+        <v>46269</v>
+      </c>
       <c r="G39" s="7"/>
-      <c r="H39" s="15"/>
+      <c r="H39" s="11">
+        <v>3090.14</v>
+      </c>
       <c r="I39" s="12">
         <v>165383.5</v>
       </c>
       <c r="J39" s="13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K39" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>49615.049999999996</v>
       </c>
       <c r="L39" s="14">
         <f t="shared" si="1"/>
-        <v>165383.5</v>
+        <v>115768.45000000001</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.2">
@@ -2536,24 +2566,28 @@
         <v>12</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F40" s="7">
+        <v>46268</v>
+      </c>
       <c r="G40" s="7"/>
-      <c r="H40" s="15"/>
+      <c r="H40" s="11">
+        <v>3057.54</v>
+      </c>
       <c r="I40" s="12">
         <v>102730.08</v>
       </c>
       <c r="J40" s="13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K40" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20546.016000000003</v>
       </c>
       <c r="L40" s="14">
         <f t="shared" si="1"/>
-        <v>102730.08</v>
+        <v>82184.063999999998</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -2634,24 +2668,28 @@
         <v>12</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="F43" s="7">
+        <v>46269</v>
+      </c>
       <c r="G43" s="7"/>
-      <c r="H43" s="15"/>
+      <c r="H43" s="11">
+        <v>841.27</v>
+      </c>
       <c r="I43" s="12">
         <v>102673.41</v>
       </c>
       <c r="J43" s="13">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5133.6705000000002</v>
       </c>
       <c r="L43" s="14">
         <f t="shared" si="1"/>
-        <v>102673.41</v>
+        <v>97539.739499999996</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -2678,11 +2716,11 @@
         <v>0</v>
       </c>
       <c r="K44" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K2:K65" si="2">IF($I44="","",$I44*$J44)</f>
         <v/>
       </c>
       <c r="L44" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L2:L65" si="3">IF($I44="","",$I44-$K44)</f>
         <v/>
       </c>
     </row>
@@ -2710,11 +2748,11 @@
         <v>0</v>
       </c>
       <c r="K45" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L45" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2742,11 +2780,11 @@
         <v>0</v>
       </c>
       <c r="K46" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L46" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2774,11 +2812,11 @@
         <v>0</v>
       </c>
       <c r="K47" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L47" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2806,11 +2844,11 @@
         <v>0</v>
       </c>
       <c r="K48" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L48" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2838,11 +2876,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L49" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2870,11 +2908,11 @@
         <v>0</v>
       </c>
       <c r="K50" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L50" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2902,11 +2940,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L51" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2934,11 +2972,11 @@
         <v>0</v>
       </c>
       <c r="K52" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L52" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2966,11 +3004,11 @@
         <v>0</v>
       </c>
       <c r="K53" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L53" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2998,11 +3036,11 @@
         <v>0</v>
       </c>
       <c r="K54" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L54" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3030,11 +3068,11 @@
         <v>0</v>
       </c>
       <c r="K55" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L55" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3062,11 +3100,11 @@
         <v>0</v>
       </c>
       <c r="K56" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L56" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3094,11 +3132,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L57" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3126,11 +3164,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L58" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3158,11 +3196,11 @@
         <v>0</v>
       </c>
       <c r="K59" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L59" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3190,11 +3228,11 @@
         <v>0</v>
       </c>
       <c r="K60" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L60" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3222,11 +3260,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L61" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3254,11 +3292,11 @@
         <v>0</v>
       </c>
       <c r="K62" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L62" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3286,11 +3324,11 @@
         <v>0</v>
       </c>
       <c r="K63" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L63" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3318,11 +3356,11 @@
         <v>0</v>
       </c>
       <c r="K64" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L64" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3350,11 +3388,11 @@
         <v>0</v>
       </c>
       <c r="K65" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L65" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3382,11 +3420,11 @@
         <v>0</v>
       </c>
       <c r="K66" s="16" t="str">
-        <f t="shared" ref="K66:K129" si="2">IF($I66="","",$I66*$J66)</f>
+        <f t="shared" ref="K66:K129" si="4">IF($I66="","",$I66*$J66)</f>
         <v/>
       </c>
       <c r="L66" s="16" t="str">
-        <f t="shared" ref="L66:L129" si="3">IF($I66="","",$I66-$K66)</f>
+        <f t="shared" ref="L66:L129" si="5">IF($I66="","",$I66-$K66)</f>
         <v/>
       </c>
     </row>
@@ -3414,11 +3452,11 @@
         <v>0</v>
       </c>
       <c r="K67" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L67" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3446,11 +3484,11 @@
         <v>0</v>
       </c>
       <c r="K68" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L68" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3478,11 +3516,11 @@
         <v>0</v>
       </c>
       <c r="K69" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L69" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3510,11 +3548,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L70" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3542,11 +3580,11 @@
         <v>0</v>
       </c>
       <c r="K71" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L71" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3574,11 +3612,11 @@
         <v>0</v>
       </c>
       <c r="K72" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L72" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3606,11 +3644,11 @@
         <v>0</v>
       </c>
       <c r="K73" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L73" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3638,11 +3676,11 @@
         <v>0</v>
       </c>
       <c r="K74" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L74" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3670,11 +3708,11 @@
         <v>0</v>
       </c>
       <c r="K75" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L75" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3702,11 +3740,11 @@
         <v>0</v>
       </c>
       <c r="K76" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L76" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3734,11 +3772,11 @@
         <v>0</v>
       </c>
       <c r="K77" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L77" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3766,11 +3804,11 @@
         <v>0</v>
       </c>
       <c r="K78" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L78" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3798,11 +3836,11 @@
         <v>0</v>
       </c>
       <c r="K79" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L79" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3830,11 +3868,11 @@
         <v>0</v>
       </c>
       <c r="K80" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L80" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3862,11 +3900,11 @@
         <v>0</v>
       </c>
       <c r="K81" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L81" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3894,11 +3932,11 @@
         <v>0</v>
       </c>
       <c r="K82" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L82" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3926,11 +3964,11 @@
         <v>0</v>
       </c>
       <c r="K83" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L83" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3958,11 +3996,11 @@
         <v>0</v>
       </c>
       <c r="K84" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L84" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -3990,11 +4028,11 @@
         <v>0</v>
       </c>
       <c r="K85" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L85" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4022,11 +4060,11 @@
         <v>0</v>
       </c>
       <c r="K86" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L86" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4054,11 +4092,11 @@
         <v>0</v>
       </c>
       <c r="K87" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L87" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4086,11 +4124,11 @@
         <v>0</v>
       </c>
       <c r="K88" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L88" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4118,11 +4156,11 @@
         <v>0</v>
       </c>
       <c r="K89" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L89" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4150,11 +4188,11 @@
         <v>0</v>
       </c>
       <c r="K90" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L90" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4182,11 +4220,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L91" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4214,11 +4252,11 @@
         <v>0</v>
       </c>
       <c r="K92" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L92" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4246,11 +4284,11 @@
         <v>0</v>
       </c>
       <c r="K93" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L93" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4278,11 +4316,11 @@
         <v>0</v>
       </c>
       <c r="K94" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L94" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4310,11 +4348,11 @@
         <v>0</v>
       </c>
       <c r="K95" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L95" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4342,11 +4380,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L96" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4374,11 +4412,11 @@
         <v>0</v>
       </c>
       <c r="K97" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L97" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4406,11 +4444,11 @@
         <v>0</v>
       </c>
       <c r="K98" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L98" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4438,11 +4476,11 @@
         <v>0</v>
       </c>
       <c r="K99" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L99" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4470,11 +4508,11 @@
         <v>0</v>
       </c>
       <c r="K100" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L100" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4502,11 +4540,11 @@
         <v>0</v>
       </c>
       <c r="K101" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L101" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4534,11 +4572,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L102" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4566,11 +4604,11 @@
         <v>0</v>
       </c>
       <c r="K103" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L103" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4598,11 +4636,11 @@
         <v>0</v>
       </c>
       <c r="K104" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L104" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4630,11 +4668,11 @@
         <v>0</v>
       </c>
       <c r="K105" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L105" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4662,11 +4700,11 @@
         <v>0</v>
       </c>
       <c r="K106" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L106" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4694,11 +4732,11 @@
         <v>0</v>
       </c>
       <c r="K107" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L107" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4726,11 +4764,11 @@
         <v>0</v>
       </c>
       <c r="K108" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L108" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4758,11 +4796,11 @@
         <v>0</v>
       </c>
       <c r="K109" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L109" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4790,11 +4828,11 @@
         <v>0</v>
       </c>
       <c r="K110" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L110" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4822,11 +4860,11 @@
         <v>0</v>
       </c>
       <c r="K111" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L111" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4854,11 +4892,11 @@
         <v>0</v>
       </c>
       <c r="K112" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L112" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4886,11 +4924,11 @@
         <v>0</v>
       </c>
       <c r="K113" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L113" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4918,11 +4956,11 @@
         <v>0</v>
       </c>
       <c r="K114" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L114" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4950,11 +4988,11 @@
         <v>0</v>
       </c>
       <c r="K115" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L115" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4982,11 +5020,11 @@
         <v>0</v>
       </c>
       <c r="K116" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L116" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5014,11 +5052,11 @@
         <v>0</v>
       </c>
       <c r="K117" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L117" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5046,11 +5084,11 @@
         <v>0</v>
       </c>
       <c r="K118" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L118" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5078,11 +5116,11 @@
         <v>0</v>
       </c>
       <c r="K119" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L119" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5110,11 +5148,11 @@
         <v>0</v>
       </c>
       <c r="K120" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L120" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5142,11 +5180,11 @@
         <v>0</v>
       </c>
       <c r="K121" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L121" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5174,11 +5212,11 @@
         <v>0</v>
       </c>
       <c r="K122" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L122" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5206,11 +5244,11 @@
         <v>0</v>
       </c>
       <c r="K123" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L123" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5238,11 +5276,11 @@
         <v>0</v>
       </c>
       <c r="K124" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L124" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5270,11 +5308,11 @@
         <v>0</v>
       </c>
       <c r="K125" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L125" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5302,11 +5340,11 @@
         <v>0</v>
       </c>
       <c r="K126" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L126" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5334,11 +5372,11 @@
         <v>0</v>
       </c>
       <c r="K127" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L127" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5366,11 +5404,11 @@
         <v>0</v>
       </c>
       <c r="K128" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L128" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5398,11 +5436,11 @@
         <v>0</v>
       </c>
       <c r="K129" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L129" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5430,11 +5468,11 @@
         <v>0</v>
       </c>
       <c r="K130" s="16" t="str">
-        <f t="shared" ref="K130:K164" si="4">IF($I130="","",$I130*$J130)</f>
+        <f t="shared" ref="K130:K164" si="6">IF($I130="","",$I130*$J130)</f>
         <v/>
       </c>
       <c r="L130" s="16" t="str">
-        <f t="shared" ref="L130:L164" si="5">IF($I130="","",$I130-$K130)</f>
+        <f t="shared" ref="L130:L164" si="7">IF($I130="","",$I130-$K130)</f>
         <v/>
       </c>
     </row>
@@ -5462,11 +5500,11 @@
         <v>0</v>
       </c>
       <c r="K131" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L131" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5494,11 +5532,11 @@
         <v>0</v>
       </c>
       <c r="K132" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L132" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5526,11 +5564,11 @@
         <v>0</v>
       </c>
       <c r="K133" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L133" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5558,11 +5596,11 @@
         <v>0</v>
       </c>
       <c r="K134" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L134" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5590,11 +5628,11 @@
         <v>0</v>
       </c>
       <c r="K135" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L135" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5622,11 +5660,11 @@
         <v>0</v>
       </c>
       <c r="K136" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L136" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5654,11 +5692,11 @@
         <v>0</v>
       </c>
       <c r="K137" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L137" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5686,11 +5724,11 @@
         <v>0</v>
       </c>
       <c r="K138" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L138" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5718,11 +5756,11 @@
         <v>0</v>
       </c>
       <c r="K139" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L139" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5750,11 +5788,11 @@
         <v>0</v>
       </c>
       <c r="K140" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L140" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5782,11 +5820,11 @@
         <v>0</v>
       </c>
       <c r="K141" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L141" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5814,11 +5852,11 @@
         <v>0</v>
       </c>
       <c r="K142" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L142" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5846,11 +5884,11 @@
         <v>0</v>
       </c>
       <c r="K143" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L143" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5878,11 +5916,11 @@
         <v>0</v>
       </c>
       <c r="K144" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L144" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5910,11 +5948,11 @@
         <v>0</v>
       </c>
       <c r="K145" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L145" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5942,11 +5980,11 @@
         <v>0</v>
       </c>
       <c r="K146" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L146" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5974,11 +6012,11 @@
         <v>0</v>
       </c>
       <c r="K147" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L147" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6006,11 +6044,11 @@
         <v>0</v>
       </c>
       <c r="K148" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L148" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6038,11 +6076,11 @@
         <v>0</v>
       </c>
       <c r="K149" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L149" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6070,11 +6108,11 @@
         <v>0</v>
       </c>
       <c r="K150" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L150" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6102,11 +6140,11 @@
         <v>0</v>
       </c>
       <c r="K151" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L151" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6134,11 +6172,11 @@
         <v>0</v>
       </c>
       <c r="K152" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L152" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6166,11 +6204,11 @@
         <v>0</v>
       </c>
       <c r="K153" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L153" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6198,11 +6236,11 @@
         <v>0</v>
       </c>
       <c r="K154" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L154" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6230,11 +6268,11 @@
         <v>0</v>
       </c>
       <c r="K155" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L155" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6262,11 +6300,11 @@
         <v>0</v>
       </c>
       <c r="K156" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L156" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6294,11 +6332,11 @@
         <v>0</v>
       </c>
       <c r="K157" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L157" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6326,11 +6364,11 @@
         <v>0</v>
       </c>
       <c r="K158" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L158" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6358,11 +6396,11 @@
         <v>0</v>
       </c>
       <c r="K159" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L159" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6390,11 +6428,11 @@
         <v>0</v>
       </c>
       <c r="K160" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L160" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6422,11 +6460,11 @@
         <v>0</v>
       </c>
       <c r="K161" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L161" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6454,11 +6492,11 @@
         <v>0</v>
       </c>
       <c r="K162" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L162" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6486,11 +6524,11 @@
         <v>0</v>
       </c>
       <c r="K163" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L163" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6518,11 +6556,11 @@
         <v>0</v>
       </c>
       <c r="K164" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="L164" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>

--- a/Ruas de Bauru.xlsx
+++ b/Ruas de Bauru.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/09f6c07718b65a17/Trabalho/ATA Bauru/Site Recape Bauru/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CCB57FE-EF21-3A4C-87EB-8CDB066B39BD}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{9256A3C2-1EE2-40DA-B6AF-1F238AD001AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A15C5D-1E00-0341-934A-924C195961E0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,13 +633,13 @@
     <t>24/08/206</t>
   </si>
   <si>
-    <t>Valor Ago.26 (R$)</t>
-  </si>
-  <si>
     <t>Saldo a Medir (R$)</t>
   </si>
   <si>
     <t>Paralisada</t>
+  </si>
+  <si>
+    <t>Valor Executado (R$)</t>
   </si>
 </sst>
 </file>
@@ -1110,10 +1110,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -2464,7 +2464,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -2496,7 +2496,7 @@
         <v>12</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -2604,7 +2604,7 @@
         <v>12</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -2636,7 +2636,7 @@
         <v>12</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -2706,7 +2706,7 @@
         <v>12</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -2716,11 +2716,11 @@
         <v>0</v>
       </c>
       <c r="K44" s="14" t="str">
-        <f t="shared" ref="K2:K65" si="2">IF($I44="","",$I44*$J44)</f>
+        <f t="shared" ref="K44:K65" si="2">IF($I44="","",$I44*$J44)</f>
         <v/>
       </c>
       <c r="L44" s="14" t="str">
-        <f t="shared" ref="L2:L65" si="3">IF($I44="","",$I44-$K44)</f>
+        <f t="shared" ref="L44:L65" si="3">IF($I44="","",$I44-$K44)</f>
         <v/>
       </c>
     </row>

--- a/Ruas de Bauru.xlsx
+++ b/Ruas de Bauru.xlsx
@@ -879,10 +879,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
